--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Deck Equipment for Research &amp; Survey Vessels | RTG</t>
+          <t>Deck Machinery for Research, Survey &amp; Offshore Vessels | RTG</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Custom winches, launch and recovery systems and deck machinery for research, survey and geotechnical vessels. Designed in the UK, built and tested in the EU.</t>
+          <t>Custom winches, LARS, tensioners and cranes for research, survey and offshore vessels. Family business since 1978. Designed in the UK, built and tested in the EU.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Deck equipment built for the work, not the brochure</t>
+          <t>Custom deck machinery for research, survey and offshore vessels</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sectors We Supply | Survey, Geotechnical, Wind | RTG</t>
+          <t>Sectors | Survey, Geotechnical, Wind, Seismic, Subsea | RTG</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>RTG deck equipment works across ocean survey, marine geotechnical, offshore wind and cables, seismic, research, subsea and defence. Find your sector.</t>
+          <t>RTG deck machinery for ocean survey, marine geotechnical, offshore wind and cables, seismic, oceanographic research, subsea and defence vessels.</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The sectors we build for</t>
+          <t>Deck handling systems for seven offshore sectors</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Winches and launch and recovery systems for hydrographic and geophysical survey: CTD, side scan, magnetometer, sub-bottom profiler and deep tow, 300 to 4,000 m.</t>
+          <t>Winches and LARS for hydrographic and geophysical survey: CTD, side scan, magnetometer, sub-bottom profiler and deep tow, 300 to 4,000 m.</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Handling systems for survey and hydrographic work</t>
+          <t>Survey and hydrographic handling systems</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Corer, CPT and vibrocorer handling systems with tension control for seabed sampling. Proven to a 3,000 m working depth on a CPT sampling system.</t>
+          <t>Corer, CPT and vibrocorer handling systems with constant tension control for seabed sampling. Proven to 3,000 m working depth on a CPT sampling system.</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>When the tool is fixed to the seabed and the ship is not</t>
+          <t>Geotechnical handling systems, proven to 3,000 m</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Site investigation handling, cable tensioners from 5 to 20 tonnes and containerised cable spreads for offshore wind arrays, export cables and interconnectors.</t>
+          <t>Site-investigation handling, 5 to 20 tonne cable tensioners and containerised cable spreads for offshore wind arrays, export cables and interconnectors.</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Every turbine starts with a core sample. Every array ends with a cable.</t>
+          <t>Site investigation and cable handling for offshore wind</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Seismic winches, source handling and streamer deployment systems for 2D and 3D marine seismic acquisition, designed for continuous duty at sea.</t>
+          <t>Seismic winches, source handling and streamer deployment systems for 2D and 3D marine seismic acquisition, designed for continuous duty.</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Seismic handling built for continuous duty</t>
+          <t>Seismic handling for continuous duty</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Research winches for CTD, coring and deep tow work, from 300 to 4,000 m, electric or hydraulic, with precise slow-speed control for repeatable casts.</t>
+          <t>Research winches for CTD, coring and deep-tow work, 300 to 4,000 m, electric or hydraulic, with precise slow-speed control for repeatable casts.</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>A CTD cast is a measurement, not a lift</t>
+          <t>Research winches for precise, repeatable casts</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>An ROV is only as available as its umbilical winch</t>
+          <t>ROV, umbilical and personnel handling systems</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Deck machinery and handling systems for naval, coastguard and government research vessels, built to class with full material and weld traceability.</t>
+          <t>Deck machinery for naval, coastguard and government research vessels, built to class with full material and weld traceability.</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Built for government and naval programmes</t>
+          <t>Deck machinery for naval and government programmes</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The RTG equipment range: winches, launch and recovery systems, cranes, handling systems, power units and containerised spreads for survey and subsea work.</t>
+          <t>The RTG range: winches, launch and recovery systems, cranes, tensioners, power units and containerised spreads for survey and subsea work.</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The equipment range</t>
+          <t>Equipment range</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Marine Winches | Survey, Geotechnical &amp; ROV | RTG</t>
+          <t>Marine Winches | Survey, Geotechnical, Seismic &amp; ROV | RTG</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Electric and hydraulic marine winches from 0.3 to 7.4 tonnes working load and 200 to 5,500 m capacity, with Lebus grooved drums and controlled level wind.</t>
+          <t>Electric and hydraulic marine winches from 240 kg to 30 t WLL and up to 3,500 m capacity, with Lebus grooved drums and controlled level wind.</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Winches</t>
+          <t>Marine winches, 240 kg to 30 t WLL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Winches for piston, gravity and box coring and CPT deployment, with constant tension control to protect the umbilical when the tool is captive in the seabed.</t>
+          <t>Winches for piston, gravity and box coring and CPT deployment, with constant tension control to protect the umbilical.</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Survey &amp; Oceanographic Winches | 300-4,000 m | RTG</t>
+          <t>Survey &amp; Oceanographic Winches | 300 to 4,000 m | RTG</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Survey and oceanographic winches in electric or hydraulic drive, with or without level wind, supplied with cable capacities from 300 to 4,000 metres.</t>
+          <t>Survey and oceanographic winches in electric or hydraulic drive, with or without level wind, with cable capacities from 300 to 4,000 metres.</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Seismic winches and source handling equipment engineered for continuous duty, high line speeds and repeated deployment cycles in marine acquisition.</t>
+          <t>Seismic winches and source handling equipment for continuous duty, high line speeds and repeated deployment cycles in marine acquisition.</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ROV, Tow &amp; Umbilical Winches | Slip Ring Ready | RTG</t>
+          <t>ROV, Tow &amp; Umbilical Winches | RTG</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ROV, deep tow and umbilical winches with Lebus grooved drums, controlled level wind and a slip ring interface to suit your own data and power architecture.</t>
+          <t>ROV, deep-tow and umbilical winches with Lebus grooved drums, controlled level wind and a slip ring interface to suit your data and power architecture.</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mooring, capstan and general utility winches for offshore and research vessels, built to class with the same welding and test discipline as the survey range.</t>
+          <t>Mooring, towing and utility winches for offshore and research vessels, built to class with full weld traceability and proof load testing.</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Stern and side A-frames, mini survey LARS, ROV and CTD launch and recovery systems, engineered around your deck arrangement and sea state requirement.</t>
+          <t>Stern and side A-frames, ROV and CTD launch and recovery systems, 20 to 40 Te WLL, rated to 3.9 m significant wave height.</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Launch and recovery systems</t>
+          <t>A-frames and LARS rated to 3.9 m Hs</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Deck cranes, knuckle boom and telescopic lifting equipment for research and offshore vessels, class certified and proof tested before dispatch.</t>
+          <t>Knuckle boom, telescopic and utility deck cranes, davits and personnel-rated lifting for research and offshore vessels, class certified and proof tested.</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Cranes and lifting equipment</t>
+          <t>Deck cranes and lifting equipment</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Complete handling systems for corers, seismic sources, diver baskets and subsea cable, supplied as integrated deck spreads rather than individual machines.</t>
+          <t>Complete handling systems for corers, seismic sources, diver baskets and subsea cable, supplied as integrated deck spreads.</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Self-contained two-track electro-hydraulic tensioners from 5 to 20 tonnes on a common skid, remote console controlled, for cable and pipe laying operations.</t>
+          <t>Self-contained two-track electro-hydraulic tensioners from 5 to 20 tonnes on a common skid, remote console controlled, for cable and pipe lay.</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Cable and pipe tensioners</t>
+          <t>Two-track tensioners, 5 to 20 Te</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Hydraulic power units for deck machinery, built and flushed to a defined cleanliness class and function tested with the equipment they will drive.</t>
+          <t>Hydraulic power units for deck machinery, flushed to a defined cleanliness class and function tested with the equipment they drive.</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Self-contained, road transportable handling spreads with certified lifting lugs, fork pockets and twist-lock footprints, for vessels you do not own.</t>
+          <t>Self-contained, road-transportable handling spreads with certified lifting lugs, fork pockets and twist-lock footprints for chartered vessels.</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Built to move between hulls</t>
+          <t>Portable and containerised spreads</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Your vessel is worth more working than replaced. Condition assessment, refurbishment, capability upgrade, re-certification and spares for deck machinery.</t>
+          <t>Condition assessment, refurbishment, upgrade, re-certification and spares for deck machinery, including equipment from other manufacturers.</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Keeping equipment working</t>
+          <t>Supported for the full service life</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Full refurbishment of winches, LARS and deck machinery: condition assessment, rework, component reuse, capability upgrade, testing and reissued documentation.</t>
+          <t>Refurbishment of winches, LARS and deck machinery: condition assessment, component reuse, capability upgrade, load testing and reissued documentation.</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Six questions that decide whether deck machinery is worth rebuilding: drum and shaft condition, brakes, hydraulics, capability target, spares and class status.</t>
+          <t>Six factors that decide whether deck machinery is worth rebuilding: drum and shaft, brakes, hydraulics, capability, spares and class status.</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Refurbish, upgrade or replace?</t>
+          <t>Refurbish, upgrade or replace: six factors</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Load testing, inspection and documentation for class renewal on deck machinery, including equipment originally supplied by other manufacturers.</t>
+          <t>Load testing, inspection and documentation for class renewal on deck machinery, including equipment supplied by other manufacturers.</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Spares, technical support and field service for RTG equipment and for deck machinery supplied by others, through UK and EU offices and agents worldwide.</t>
+          <t>Spares, technical support and field service for RTG equipment and deck machinery from other manufacturers, through UK and EU offices and agents worldwide.</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tell us the equipment, the vessel and the maintenance window. We will tell you what is worth rebuilding, what is not, and what the work would involve.</t>
+          <t>Book a condition assessment for winches, LARS and deck machinery. Written report with reuse, rework and replace recommendations and costed options.</t>
         </is>
       </c>
       <c r="L29" t="n">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Your design, your IP, our factory. From welded structures to complete machines, assembled, piped, wired, programmed, load tested under class and commissioned.</t>
+          <t>Your design, your IP, our factory. Structural fabrication to complete machines: assembled, piped, wired, programmed, load tested under class and commissioned.</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>How much of your machine would you like us to take?</t>
+          <t>Contract manufacturing</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Welded structures to your drawings with EN ISO 3834 discipline, coded welders, NDT to ISO 9712 level 2 and 100 percent traceability on structural welds.</t>
+          <t>Welded structures to your drawings with EN ISO 3834 discipline, coded welders, NDT to ISO 9712 level 2 and 100% traceability on structural welds.</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Drums, shafts, bearings, gearboxes, brakes, sheaves and level wind assembled to your specification, torqued, aligned and rotation checked before dispatch.</t>
+          <t>Drums, shafts, bearings, gearboxes, brakes, sheaves and level wind assembled to your specification, torqued, aligned and rotation checked.</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Power units, pipework flushed to a defined cleanliness class, valve blocks, control panels, cabling, terminations and instrumentation, built to your schematics.</t>
+          <t>Power units, pipework flushed to a defined cleanliness class, valve blocks, control panels, cabling and instrumentation, built to your schematics.</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>PLC and HMI loading, interlock proving, load testing to 150 tonnes under class witness, full certification dossier and commissioning on the vessel.</t>
+          <t>PLC and HMI loading, interlock proving, load testing to 150 tonnes under class witness, full certification dossier and vessel commissioning.</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NDA before drawings, segregated project files, no derivative products from client designs, and a clear contractual separation from our own equipment range.</t>
+          <t>NDA before drawings, segregated project files, no derivative products from client designs, and contractual separation from our own equipment range.</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Your design stays yours</t>
+          <t>Design and IP protection</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Fabrication inside the EU, with melt-and-pour origin documentation supplied alongside our standard weld traceability pack for every structure we build.</t>
+          <t>Fabrication inside the EU, with melt-and-pour origin documentation supplied with our standard weld traceability pack.</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Fabricated inside the EU, documented</t>
+          <t>EU-origin fabrication</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A quarterly statement of available fabrication, assembly, hydraulic build and test capacity by tier, with indicative lead times for each. Updated every quarter.</t>
+          <t>Quarterly statement of available fabrication, assembly, hydraulic build and test capacity by tier, with indicative lead times.</t>
         </is>
       </c>
       <c r="L38" t="n">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -4637,7 +4637,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Subcontract Fabrication &amp; Deck Packages for Yards | RTG</t>
+          <t>Subcontract Fabrication &amp; Deck Packages for Shipyards | RTG</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>European standards, EU capacity, class certified. Overflow structural fabrication and deck equipment packages that protect your delivery date.</t>
+          <t>EU capacity, class certified. Overflow structural fabrication and complete deck-equipment packages delivered to your build programme.</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Capacity that protects your delivery date</t>
+          <t>Class-certified capacity for shipyard programmes</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Complete deck handling packages specified, built, tested and commissioned for newbuild survey, research and offshore vessels, integrated with your programme.</t>
+          <t>Complete deck handling packages engineered, built, tested and commissioned for newbuild survey, research and offshore vessels.</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Deck equipment packages</t>
+          <t>Deck-equipment packages for newbuilds</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Bureau Veritas Mode II recognition, welding procedures approved with TUV, DNV and Lloyd's Register, welders to ISO 9606-1 and NDT to ISO 9712 level 2.</t>
+          <t>Bureau Veritas Mode II recognition, welding procedures approved with TÜV, DNV and Lloyd's Register, welders to ISO 9606-1 and NDT to ISO 9712 level 2.</t>
         </is>
       </c>
       <c r="L43" t="n">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -5175,7 +5175,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Twenty-two years, more than 250 completed projects and around 1,500 deck machines. Case studies, vessel references, our test facility and what clients say.</t>
+          <t>Family business since 1978: more than 250 completed projects and around 1,500 deck machines. Case studies, references and our test facility.</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>The evidence</t>
+          <t>Track record</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>How RTG standardised handling across a survey fleet, rebuilt a twelve-year-old traction winch, and built complete machines to an OEM's drawings.</t>
+          <t>Fleet standardisation across seven Fugro vessels, a rebuilt 2009 traction winch, contract manufacturing and a shipyard newbuild programme.</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A twelve-year-old electro-hydraulic traction winch assessed, rebuilt, upgraded and retested for offshore geotechnical work, with documentation reissued.</t>
+          <t>A 2009 electro-hydraulic traction winch assessed, rebuilt, upgraded and retested for offshore geotechnical work, with documentation reissued.</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>The winch we built in 2009, rebuilt in 2021</t>
+          <t>2009 traction winch, rebuilt in 2021</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Two test stands, load testing to 150 tonnes with certified weights: proof load, dynamic functional, brake holding, render and speed tests under class witness.</t>
+          <t>Two test stands, load testing to 150 tonnes with certified weights: proof load, dynamic, brake holding, render and speed tests under class witness.</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Nothing leaves this factory untested</t>
+          <t>Test facility: two stands, 150 Te</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>More than 50 global customers and research institutions, over 250 completed projects and around 1,500 custom deck machines delivered since 2003.</t>
+          <t>More than 50 operators, OEMs, shipyards and research institutions; over 250 projects and around 1,500 custom deck machines since 1978.</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Vessels and clients</t>
+          <t>Clients</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>In the words of a global survey operator, a major shipyard and an offshore equipment specialist, on design quality, communication and on-time delivery.</t>
+          <t>Operators, shipyards and equipment manufacturers on RTG's design quality, communication and on-time delivery.</t>
         </is>
       </c>
       <c r="L53" t="n">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -6545,7 +6545,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>About RTG | British Design, European Manufacture</t>
+          <t>About RTG | Family Business in Deck Machinery Since 1978</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Founded to combine British deck equipment design with European manufacturing. Twenty-two years, 250 projects and around 1,500 machines delivered.</t>
+          <t>Family-owned since 1978. British deck machinery design and European manufacturing: 1,500 machines and 250 projects for 50+ clients.</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>A father, a son, and a factory in Satu Mare</t>
+          <t>A family business in deck machinery since 1978</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Around 80 engineers, welders, fitters and technicians in a purpose-built facility in Satu Mare, Romania, with design and commercial teams in the UK.</t>
+          <t>Around 80 engineers, welders, fitters and technicians in Satu Mare, Romania, with design and commercial teams in the UK.</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>The people and the place</t>
+          <t>People and facility</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Welding, mechanical, hydraulic, electrical, automation and design roles in Satu Mare and the UK. See what we build and who you would build it with.</t>
+          <t>Welding, mechanical, hydraulic, electrical, automation and design roles in Satu Mare and the UK.</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Build things that go to sea</t>
+          <t>Careers</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Talk to our UK commercial team or our factory at Satu Mare in Romania, or find your regional agent across the Americas and Asia Pacific. We answer quickly.</t>
+          <t>Contact our UK commercial team or our Satu Mare factory, or find your regional agent in the Americas and Asia Pacific.</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Contact us</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Our Agents in the Americas and Asia Pacific | RTG</t>
+          <t>RTG Agents in the Americas and Asia Pacific | RTG</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Local representation for sales, support and spares across the Americas and Asia Pacific, backed directly by the engineers who designed and built the equipment.</t>
+          <t>Local sales, support and spares in the Americas and Asia Pacific, backed by the engineers who designed and built the equipment.</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Where to find us</t>
+          <t>Agents</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Tell us the duty, the vessel and the timescale. We will come back with a proposed configuration and an indicative price, and say what we still need.</t>
+          <t>Send the duty, vessel and timescale for a proposed configuration and indicative price.</t>
         </is>
       </c>
       <c r="L65" t="n">

--- a/RTG_Website/research/RTG_Website_Page_Map.xlsx
+++ b/RTG_Website/research/RTG_Website_Page_Map.xlsx
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Electric and hydraulic marine winches from 240 kg to 30 t WLL and up to 3,500 m capacity, with Lebus grooved drums and controlled level wind.</t>
+          <t>Electric and hydraulic marine winches from 240 kg to 48 t WLL and up to 3,500 m capacity, with Lebus grooved drums and controlled level wind.</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Marine winches, 240 kg to 30 t WLL</t>
+          <t>Marine winches, 240 kg to 48 t WLL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Stern and side A-frames, ROV and CTD launch and recovery systems, 20 to 40 Te WLL, rated to 3.9 m significant wave height.</t>
+          <t>Stern and side A-frames, ROV and CTD launch and recovery systems, 5 to 40 Te WLL, rated to 3.9 m significant wave height.</t>
         </is>
       </c>
       <c r="L18" t="n">
